--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,216 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E8" s="3">
         <v>7100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>4100</v>
       </c>
       <c r="R8" s="3">
         <v>4100</v>
       </c>
       <c r="S8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T8" s="3">
         <v>4300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>3800</v>
       </c>
       <c r="W8" s="3">
         <v>3800</v>
       </c>
       <c r="X8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y8" s="3">
         <v>3700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>1800</v>
       </c>
       <c r="AD8" s="3">
         <v>1800</v>
@@ -873,8 +877,11 @@
       <c r="AE8" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,8 +969,11 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1398,8 +1421,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>5</v>
@@ -1416,15 +1439,15 @@
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-200</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,64 +1496,65 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>500</v>
       </c>
       <c r="I17" s="3">
         <v>500</v>
       </c>
       <c r="J17" s="3">
+        <v>500</v>
+      </c>
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>800</v>
       </c>
       <c r="P17" s="3">
         <v>800</v>
       </c>
       <c r="Q17" s="3">
+        <v>800</v>
+      </c>
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2400</v>
-      </c>
-      <c r="U17" s="3">
-        <v>800</v>
       </c>
       <c r="V17" s="3">
         <v>800</v>
@@ -1536,90 +1563,93 @@
         <v>800</v>
       </c>
       <c r="X17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Y17" s="3">
         <v>700</v>
       </c>
       <c r="Z17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AA17" s="3">
         <v>500</v>
       </c>
       <c r="AB17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AC17" s="3">
         <v>400</v>
       </c>
       <c r="AD17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E18" s="3">
         <v>5200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>4000</v>
       </c>
       <c r="K18" s="3">
         <v>4000</v>
       </c>
       <c r="L18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M18" s="3">
         <v>3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>3000</v>
       </c>
       <c r="W18" s="3">
         <v>3000</v>
@@ -1628,28 +1658,31 @@
         <v>3000</v>
       </c>
       <c r="Y18" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="Z18" s="3">
         <v>2800</v>
       </c>
       <c r="AA18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AB18" s="3">
         <v>2300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>1500</v>
       </c>
       <c r="AE18" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,67 +1714,68 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2500</v>
       </c>
       <c r="G20" s="3">
         <v>-2500</v>
       </c>
       <c r="H20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-2200</v>
       </c>
       <c r="K20" s="3">
         <v>-2200</v>
       </c>
       <c r="L20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q20" s="3">
         <v>-2000</v>
       </c>
       <c r="R20" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="S20" s="3">
         <v>-1900</v>
       </c>
       <c r="T20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U20" s="3">
         <v>-3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-2000</v>
       </c>
       <c r="W20" s="3">
         <v>-2000</v>
@@ -1753,25 +1787,28 @@
         <v>-2000</v>
       </c>
       <c r="Z20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1859,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,19 +1988,22 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="E23" s="3">
         <v>2400</v>
       </c>
       <c r="F23" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="G23" s="3">
         <v>1900</v>
@@ -1969,120 +2012,123 @@
         <v>1900</v>
       </c>
       <c r="I23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J23" s="3">
         <v>1400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1800</v>
       </c>
       <c r="K23" s="3">
         <v>1800</v>
       </c>
       <c r="L23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>1400</v>
       </c>
       <c r="P23" s="3">
         <v>1400</v>
       </c>
       <c r="Q23" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="R23" s="3">
         <v>1100</v>
       </c>
       <c r="S23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1100</v>
       </c>
       <c r="W23" s="3">
         <v>1100</v>
       </c>
       <c r="X23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
         <v>600</v>
       </c>
       <c r="F24" s="3">
+        <v>600</v>
+      </c>
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>400</v>
       </c>
       <c r="P24" s="3">
         <v>400</v>
       </c>
       <c r="Q24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
@@ -2091,43 +2137,46 @@
         <v>300</v>
       </c>
       <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>600</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
       <c r="W24" s="3">
+        <v>300</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,43 +2264,46 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1000</v>
       </c>
       <c r="O26" s="3">
         <v>1000</v>
@@ -2260,22 +2312,22 @@
         <v>1000</v>
       </c>
       <c r="Q26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="R26" s="3">
         <v>800</v>
       </c>
       <c r="S26" s="3">
+        <v>800</v>
+      </c>
+      <c r="T26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>800</v>
       </c>
       <c r="W26" s="3">
         <v>800</v>
@@ -2284,13 +2336,13 @@
         <v>800</v>
       </c>
       <c r="Y26" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>100</v>
       </c>
       <c r="AB26" s="3">
         <v>100</v>
@@ -2299,48 +2351,51 @@
         <v>100</v>
       </c>
       <c r="AD26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1000</v>
       </c>
       <c r="O27" s="3">
         <v>1000</v>
@@ -2349,22 +2404,22 @@
         <v>1000</v>
       </c>
       <c r="Q27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="R27" s="3">
         <v>800</v>
       </c>
       <c r="S27" s="3">
+        <v>800</v>
+      </c>
+      <c r="T27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>800</v>
       </c>
       <c r="W27" s="3">
         <v>800</v>
@@ -2373,13 +2428,13 @@
         <v>800</v>
       </c>
       <c r="Y27" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>100</v>
       </c>
       <c r="AB27" s="3">
         <v>100</v>
@@ -2388,13 +2443,16 @@
         <v>100</v>
       </c>
       <c r="AD27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2535,8 +2596,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
@@ -2553,8 +2614,8 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,67 +2816,70 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2500</v>
       </c>
       <c r="G32" s="3">
         <v>2500</v>
       </c>
       <c r="H32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>2200</v>
       </c>
       <c r="K32" s="3">
         <v>2200</v>
       </c>
       <c r="L32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>2000</v>
       </c>
       <c r="Q32" s="3">
         <v>2000</v>
       </c>
       <c r="R32" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="S32" s="3">
         <v>1900</v>
       </c>
       <c r="T32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U32" s="3">
         <v>3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
-      </c>
-      <c r="V32" s="3">
-        <v>2000</v>
       </c>
       <c r="W32" s="3">
         <v>2000</v>
@@ -2821,60 +2891,63 @@
         <v>2000</v>
       </c>
       <c r="Z32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>1000</v>
       </c>
       <c r="O33" s="3">
         <v>1000</v>
@@ -2883,22 +2956,22 @@
         <v>1000</v>
       </c>
       <c r="Q33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="R33" s="3">
         <v>800</v>
       </c>
       <c r="S33" s="3">
+        <v>800</v>
+      </c>
+      <c r="T33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1000</v>
-      </c>
-      <c r="V33" s="3">
-        <v>800</v>
       </c>
       <c r="W33" s="3">
         <v>800</v>
@@ -2907,13 +2980,13 @@
         <v>800</v>
       </c>
       <c r="Y33" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>100</v>
       </c>
       <c r="AB33" s="3">
         <v>100</v>
@@ -2922,13 +2995,16 @@
         <v>100</v>
       </c>
       <c r="AD33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,43 +3092,46 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>1000</v>
       </c>
       <c r="O35" s="3">
         <v>1000</v>
@@ -3061,22 +3140,22 @@
         <v>1000</v>
       </c>
       <c r="Q35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="R35" s="3">
         <v>800</v>
       </c>
       <c r="S35" s="3">
+        <v>800</v>
+      </c>
+      <c r="T35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1000</v>
-      </c>
-      <c r="V35" s="3">
-        <v>800</v>
       </c>
       <c r="W35" s="3">
         <v>800</v>
@@ -3085,13 +3164,13 @@
         <v>800</v>
       </c>
       <c r="Y35" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>100</v>
       </c>
       <c r="AB35" s="3">
         <v>100</v>
@@ -3100,107 +3179,113 @@
         <v>100</v>
       </c>
       <c r="AD35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E41" s="3">
         <v>38700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>57300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>39800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>60900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>20200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>25600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>120400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>162500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3377,48 +3467,48 @@
       <c r="I42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K42" s="3">
         <v>48800</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="3">
         <v>49400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3">
         <v>17800</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
         <v>16100</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3437,14 +3527,17 @@
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>8300</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3710,8 +3809,11 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +3993,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3911,57 +4019,57 @@
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>9200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>9400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>8700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>7500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>62300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>57400</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3971,14 +4079,17 @@
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>6700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3986,7 +4097,7 @@
         <v>1700</v>
       </c>
       <c r="E49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="F49" s="3">
         <v>1800</v>
@@ -3995,22 +4106,22 @@
         <v>1800</v>
       </c>
       <c r="H49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="I49" s="3">
         <v>1900</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2000</v>
+      <c r="J49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L49" s="3">
         <v>2000</v>
       </c>
       <c r="M49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="N49" s="3">
         <v>2100</v>
@@ -4019,7 +4130,7 @@
         <v>2100</v>
       </c>
       <c r="P49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="Q49" s="3">
         <v>2200</v>
@@ -4028,7 +4139,7 @@
         <v>2200</v>
       </c>
       <c r="S49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="T49" s="3">
         <v>2300</v>
@@ -4037,23 +4148,23 @@
         <v>2300</v>
       </c>
       <c r="V49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="W49" s="3">
         <v>2400</v>
       </c>
       <c r="X49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y49" s="3">
         <v>66100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>56300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2600</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4267,57 +4387,57 @@
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>5900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2500</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4327,14 +4447,17 @@
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>3400</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>513300</v>
+      </c>
+      <c r="E54" s="3">
         <v>510600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>500200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>471600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>473800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>460300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>457900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>420700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>423300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>418300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>406300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>402200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>414800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>377200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>352600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>360000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>368700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>353300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>345000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>354000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2481700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2299400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>356000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>333700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>227900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>223900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>219500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4666,8 +4797,11 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4778,36 +4915,36 @@
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>3000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4823,8 +4960,8 @@
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4844,8 +4981,11 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4933,22 +5073,25 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E61" s="3">
         <v>11100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1500</v>
@@ -4957,7 +5100,7 @@
         <v>1500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4969,11 +5112,11 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>2500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4981,11 +5124,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>2500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4993,20 +5136,20 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>75200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10300</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5165,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,8 +5533,11 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5410,48 +5568,48 @@
       <c r="L66" s="3">
         <v>0</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="M66" s="3">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O66" s="3">
         <v>363500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>314900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>311200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>2195900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2040900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5461,14 +5619,17 @@
       <c r="AC66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>199700</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,8 +6027,11 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5879,48 +6053,48 @@
       <c r="I72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>35200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O72" s="3">
         <v>30800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>27500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>24500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5939,14 +6113,17 @@
       <c r="AC72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>21900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E76" s="3">
         <v>50300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43800</v>
-      </c>
-      <c r="M76" s="3">
-        <v>42800</v>
       </c>
       <c r="N76" s="3">
         <v>42800</v>
       </c>
       <c r="O76" s="3">
+        <v>42800</v>
+      </c>
+      <c r="P76" s="3">
         <v>42700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>36800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>34500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>33800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>285800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>258500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>31100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,137 +6579,143 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>1000</v>
       </c>
       <c r="O81" s="3">
         <v>1000</v>
@@ -6529,22 +6724,22 @@
         <v>1000</v>
       </c>
       <c r="Q81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="R81" s="3">
         <v>800</v>
       </c>
       <c r="S81" s="3">
+        <v>800</v>
+      </c>
+      <c r="T81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1000</v>
-      </c>
-      <c r="V81" s="3">
-        <v>800</v>
       </c>
       <c r="W81" s="3">
         <v>800</v>
@@ -6553,13 +6748,13 @@
         <v>800</v>
       </c>
       <c r="Y81" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>100</v>
       </c>
       <c r="AB81" s="3">
         <v>100</v>
@@ -6568,13 +6763,16 @@
         <v>100</v>
       </c>
       <c r="AD81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,223 +656,226 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E8" s="3">
         <v>7400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>4100</v>
       </c>
       <c r="S8" s="3">
         <v>4100</v>
       </c>
       <c r="T8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="U8" s="3">
         <v>4300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3900</v>
-      </c>
-      <c r="W8" s="3">
-        <v>3800</v>
       </c>
       <c r="X8" s="3">
         <v>3800</v>
       </c>
       <c r="Y8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z8" s="3">
         <v>3700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>1800</v>
       </c>
       <c r="AE8" s="3">
         <v>1800</v>
@@ -880,8 +883,11 @@
       <c r="AF8" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1424,8 +1446,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
@@ -1442,15 +1464,15 @@
       <c r="X15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-200</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,67 +1522,68 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>500</v>
       </c>
       <c r="J17" s="3">
         <v>500</v>
       </c>
       <c r="K17" s="3">
+        <v>500</v>
+      </c>
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
-      </c>
-      <c r="P17" s="3">
-        <v>800</v>
       </c>
       <c r="Q17" s="3">
         <v>800</v>
       </c>
       <c r="R17" s="3">
+        <v>800</v>
+      </c>
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>800</v>
       </c>
       <c r="W17" s="3">
         <v>800</v>
@@ -1566,93 +1592,96 @@
         <v>800</v>
       </c>
       <c r="Y17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Z17" s="3">
         <v>700</v>
       </c>
       <c r="AA17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AB17" s="3">
         <v>500</v>
       </c>
       <c r="AC17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD17" s="3">
         <v>400</v>
       </c>
       <c r="AE17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AF17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3600</v>
-      </c>
-      <c r="K18" s="3">
-        <v>4000</v>
       </c>
       <c r="L18" s="3">
         <v>4000</v>
       </c>
       <c r="M18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N18" s="3">
         <v>3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>3000</v>
       </c>
       <c r="X18" s="3">
         <v>3000</v>
@@ -1661,28 +1690,31 @@
         <v>3000</v>
       </c>
       <c r="Z18" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AA18" s="3">
         <v>2800</v>
       </c>
       <c r="AB18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AC18" s="3">
         <v>2300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>1500</v>
       </c>
       <c r="AF18" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,70 +1747,71 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2500</v>
       </c>
       <c r="H20" s="3">
         <v>-2500</v>
       </c>
       <c r="I20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-2200</v>
       </c>
       <c r="L20" s="3">
         <v>-2200</v>
       </c>
       <c r="M20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-2000</v>
       </c>
       <c r="R20" s="3">
         <v>-2000</v>
       </c>
       <c r="S20" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="T20" s="3">
         <v>-1900</v>
       </c>
       <c r="U20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-2000</v>
       </c>
       <c r="X20" s="3">
         <v>-2000</v>
@@ -1790,25 +1823,28 @@
         <v>-2000</v>
       </c>
       <c r="AA20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1899,8 +1935,11 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,8 +2030,11 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2000,13 +2042,13 @@
         <v>2100</v>
       </c>
       <c r="E23" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="F23" s="3">
         <v>2400</v>
       </c>
       <c r="G23" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="H23" s="3">
         <v>1900</v>
@@ -2015,123 +2057,126 @@
         <v>1900</v>
       </c>
       <c r="J23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K23" s="3">
         <v>1400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1800</v>
       </c>
       <c r="L23" s="3">
         <v>1800</v>
       </c>
       <c r="M23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1200</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1400</v>
       </c>
       <c r="Q23" s="3">
         <v>1400</v>
       </c>
       <c r="R23" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="S23" s="3">
         <v>1100</v>
       </c>
       <c r="T23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1100</v>
       </c>
       <c r="X23" s="3">
         <v>1100</v>
       </c>
       <c r="Y23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>100</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
-      </c>
-      <c r="E24" s="3">
-        <v>600</v>
       </c>
       <c r="F24" s="3">
         <v>600</v>
       </c>
       <c r="G24" s="3">
+        <v>600</v>
+      </c>
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>400</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
@@ -2140,43 +2185,46 @@
         <v>300</v>
       </c>
       <c r="U24" s="3">
+        <v>300</v>
+      </c>
+      <c r="V24" s="3">
         <v>600</v>
-      </c>
-      <c r="V24" s="3">
-        <v>300</v>
       </c>
       <c r="W24" s="3">
         <v>300</v>
       </c>
       <c r="X24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2315,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2276,37 +2327,37 @@
         <v>1600</v>
       </c>
       <c r="E26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1000</v>
       </c>
       <c r="P26" s="3">
         <v>1000</v>
@@ -2315,22 +2366,22 @@
         <v>1000</v>
       </c>
       <c r="R26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="S26" s="3">
         <v>800</v>
       </c>
       <c r="T26" s="3">
+        <v>800</v>
+      </c>
+      <c r="U26" s="3">
         <v>1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>800</v>
       </c>
       <c r="X26" s="3">
         <v>800</v>
@@ -2339,13 +2390,13 @@
         <v>800</v>
       </c>
       <c r="Z26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>100</v>
       </c>
       <c r="AC26" s="3">
         <v>100</v>
@@ -2354,13 +2405,16 @@
         <v>100</v>
       </c>
       <c r="AE26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2368,37 +2422,37 @@
         <v>1600</v>
       </c>
       <c r="E27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1000</v>
       </c>
       <c r="P27" s="3">
         <v>1000</v>
@@ -2407,22 +2461,22 @@
         <v>1000</v>
       </c>
       <c r="R27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="S27" s="3">
         <v>800</v>
       </c>
       <c r="T27" s="3">
+        <v>800</v>
+      </c>
+      <c r="U27" s="3">
         <v>1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>800</v>
       </c>
       <c r="X27" s="3">
         <v>800</v>
@@ -2431,13 +2485,13 @@
         <v>800</v>
       </c>
       <c r="Z27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>100</v>
       </c>
       <c r="AC27" s="3">
         <v>100</v>
@@ -2446,13 +2500,16 @@
         <v>100</v>
       </c>
       <c r="AE27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,8 +2659,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2617,8 +2677,8 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,70 +2885,73 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2500</v>
       </c>
       <c r="H32" s="3">
         <v>2500</v>
       </c>
       <c r="I32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>2200</v>
       </c>
       <c r="L32" s="3">
         <v>2200</v>
       </c>
       <c r="M32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N32" s="3">
         <v>2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>2000</v>
       </c>
       <c r="R32" s="3">
         <v>2000</v>
       </c>
       <c r="S32" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="T32" s="3">
         <v>1900</v>
       </c>
       <c r="U32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V32" s="3">
         <v>3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>2000</v>
       </c>
       <c r="X32" s="3">
         <v>2000</v>
@@ -2894,25 +2963,28 @@
         <v>2000</v>
       </c>
       <c r="AA32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2920,37 +2992,37 @@
         <v>1600</v>
       </c>
       <c r="E33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1000</v>
       </c>
       <c r="P33" s="3">
         <v>1000</v>
@@ -2959,22 +3031,22 @@
         <v>1000</v>
       </c>
       <c r="R33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="S33" s="3">
         <v>800</v>
       </c>
       <c r="T33" s="3">
+        <v>800</v>
+      </c>
+      <c r="U33" s="3">
         <v>1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>800</v>
       </c>
       <c r="X33" s="3">
         <v>800</v>
@@ -2983,13 +3055,13 @@
         <v>800</v>
       </c>
       <c r="Z33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>100</v>
       </c>
       <c r="AC33" s="3">
         <v>100</v>
@@ -2998,13 +3070,16 @@
         <v>100</v>
       </c>
       <c r="AE33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3170,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3104,37 +3182,37 @@
         <v>1600</v>
       </c>
       <c r="E35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1000</v>
       </c>
       <c r="P35" s="3">
         <v>1000</v>
@@ -3143,22 +3221,22 @@
         <v>1000</v>
       </c>
       <c r="R35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="S35" s="3">
         <v>800</v>
       </c>
       <c r="T35" s="3">
+        <v>800</v>
+      </c>
+      <c r="U35" s="3">
         <v>1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>800</v>
       </c>
       <c r="X35" s="3">
         <v>800</v>
@@ -3167,13 +3245,13 @@
         <v>800</v>
       </c>
       <c r="Z35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>100</v>
       </c>
       <c r="AC35" s="3">
         <v>100</v>
@@ -3182,110 +3260,116 @@
         <v>100</v>
       </c>
       <c r="AE35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,166 +3437,170 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E41" s="3">
         <v>60700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>57300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>60900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>42200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>25600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>120400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>162500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>20300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L42" s="3">
         <v>48800</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P42" s="3">
         <v>49400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="3">
         <v>17800</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>16100</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3530,14 +3619,17 @@
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>8300</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,8 +4005,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,83 +4100,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>9200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>9400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>8700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>7500</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>62300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>57400</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4082,14 +4189,17 @@
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>6700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4100,7 +4210,7 @@
         <v>1700</v>
       </c>
       <c r="F49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G49" s="3">
         <v>1800</v>
@@ -4109,22 +4219,22 @@
         <v>1800</v>
       </c>
       <c r="I49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="J49" s="3">
         <v>1900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2000</v>
+      <c r="K49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M49" s="3">
         <v>2000</v>
       </c>
       <c r="N49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="O49" s="3">
         <v>2100</v>
@@ -4133,7 +4243,7 @@
         <v>2100</v>
       </c>
       <c r="Q49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="R49" s="3">
         <v>2200</v>
@@ -4142,7 +4252,7 @@
         <v>2200</v>
       </c>
       <c r="T49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="U49" s="3">
         <v>2300</v>
@@ -4151,23 +4261,23 @@
         <v>2300</v>
       </c>
       <c r="W49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="X49" s="3">
         <v>2400</v>
       </c>
       <c r="Y49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z49" s="3">
         <v>66100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>56300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2600</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,83 +4480,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>1100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>5900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2500</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4450,14 +4569,17 @@
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>3400</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>541600</v>
+      </c>
+      <c r="E54" s="3">
         <v>513300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>510600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>500200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>471600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>473800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>460300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>457900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
         <v>420700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>423300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>418300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>406300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>402200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>414800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>377200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>352600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>360000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>368700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>353300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>345000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>354000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2481700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2299400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>356000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>333700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>227900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>223900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>219500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,8 +4930,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,62 +5025,65 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>3000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4963,8 +5099,8 @@
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4984,8 +5120,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,25 +5215,28 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>1500</v>
@@ -5103,7 +5245,7 @@
         <v>1500</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5115,11 +5257,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>2500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5127,11 +5269,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>2500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5139,20 +5281,20 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>2500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>75200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10300</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5310,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,8 +5690,11 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5571,48 +5728,48 @@
       <c r="M66" s="3">
         <v>0</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3">
         <v>363500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>314900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>311200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>2195900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2040900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5622,14 +5779,17 @@
       <c r="AD66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>199700</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,74 +6200,77 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="D72" s="3">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>35200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>30800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>27500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>24500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6116,14 +6289,17 @@
       <c r="AD72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>21900</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E76" s="3">
         <v>51100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43800</v>
-      </c>
-      <c r="N76" s="3">
-        <v>42800</v>
       </c>
       <c r="O76" s="3">
         <v>42800</v>
       </c>
       <c r="P76" s="3">
+        <v>42800</v>
+      </c>
+      <c r="Q76" s="3">
         <v>42700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>40500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>37700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>36800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>34500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>33800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>32700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>285800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>258500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>31100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>32000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6770,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6688,37 +6882,37 @@
         <v>1600</v>
       </c>
       <c r="E81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1000</v>
       </c>
       <c r="P81" s="3">
         <v>1000</v>
@@ -6727,22 +6921,22 @@
         <v>1000</v>
       </c>
       <c r="R81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="S81" s="3">
         <v>800</v>
       </c>
       <c r="T81" s="3">
+        <v>800</v>
+      </c>
+      <c r="U81" s="3">
         <v>1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>800</v>
       </c>
       <c r="X81" s="3">
         <v>800</v>
@@ -6751,13 +6945,13 @@
         <v>800</v>
       </c>
       <c r="Z81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>100</v>
       </c>
       <c r="AC81" s="3">
         <v>100</v>
@@ -6766,13 +6960,16 @@
         <v>100</v>
       </c>
       <c r="AE81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7449,8 +7665,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7795,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7851,8 +8080,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8345,8 +8590,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8685,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8527,6 +8778,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,229 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E8" s="3">
         <v>7700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4100</v>
       </c>
       <c r="T8" s="3">
         <v>4100</v>
       </c>
       <c r="U8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="V8" s="3">
         <v>4300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3900</v>
-      </c>
-      <c r="X8" s="3">
-        <v>3800</v>
       </c>
       <c r="Y8" s="3">
         <v>3800</v>
       </c>
       <c r="Z8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA8" s="3">
         <v>3700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>1800</v>
       </c>
       <c r="AF8" s="3">
         <v>1800</v>
@@ -886,8 +890,11 @@
       <c r="AG8" s="3">
         <v>1800</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1449,8 +1472,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
@@ -1467,15 +1490,15 @@
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="3">
         <v>-400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-200</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,70 +1549,71 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>500</v>
       </c>
       <c r="K17" s="3">
         <v>500</v>
       </c>
       <c r="L17" s="3">
+        <v>500</v>
+      </c>
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>800</v>
       </c>
       <c r="R17" s="3">
         <v>800</v>
       </c>
       <c r="S17" s="3">
+        <v>800</v>
+      </c>
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>800</v>
       </c>
       <c r="X17" s="3">
         <v>800</v>
@@ -1595,96 +1622,99 @@
         <v>800</v>
       </c>
       <c r="Z17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AA17" s="3">
         <v>700</v>
       </c>
       <c r="AB17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AC17" s="3">
         <v>500</v>
       </c>
       <c r="AD17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AE17" s="3">
         <v>400</v>
       </c>
       <c r="AF17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AG17" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>4000</v>
       </c>
       <c r="M18" s="3">
         <v>4000</v>
       </c>
       <c r="N18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O18" s="3">
         <v>3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3100</v>
-      </c>
-      <c r="X18" s="3">
-        <v>3000</v>
       </c>
       <c r="Y18" s="3">
         <v>3000</v>
@@ -1693,28 +1723,31 @@
         <v>3000</v>
       </c>
       <c r="AA18" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AB18" s="3">
         <v>2800</v>
       </c>
       <c r="AC18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AD18" s="3">
         <v>2300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>1500</v>
       </c>
       <c r="AG18" s="3">
         <v>1500</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1757,64 +1791,64 @@
         <v>-2900</v>
       </c>
       <c r="E20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2500</v>
       </c>
       <c r="I20" s="3">
         <v>-2500</v>
       </c>
       <c r="J20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2200</v>
       </c>
       <c r="M20" s="3">
         <v>-2200</v>
       </c>
       <c r="N20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-2000</v>
       </c>
       <c r="S20" s="3">
         <v>-2000</v>
       </c>
       <c r="T20" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="U20" s="3">
         <v>-1900</v>
       </c>
       <c r="V20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-2000</v>
       </c>
       <c r="Y20" s="3">
         <v>-2000</v>
@@ -1826,25 +1860,28 @@
         <v>-2000</v>
       </c>
       <c r="AB20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1938,8 +1975,11 @@
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,25 +2073,28 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E23" s="3">
         <v>2100</v>
       </c>
       <c r="F23" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="G23" s="3">
         <v>2400</v>
       </c>
       <c r="H23" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="I23" s="3">
         <v>1900</v>
@@ -2060,76 +2103,79 @@
         <v>1900</v>
       </c>
       <c r="K23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L23" s="3">
         <v>1400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1800</v>
       </c>
       <c r="M23" s="3">
         <v>1800</v>
       </c>
       <c r="N23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O23" s="3">
         <v>1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1400</v>
       </c>
       <c r="R23" s="3">
         <v>1400</v>
       </c>
       <c r="S23" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="T23" s="3">
         <v>1100</v>
       </c>
       <c r="U23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1100</v>
       </c>
       <c r="Y23" s="3">
         <v>1100</v>
       </c>
       <c r="Z23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>100</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2137,49 +2183,49 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>600</v>
       </c>
       <c r="G24" s="3">
         <v>600</v>
       </c>
       <c r="H24" s="3">
+        <v>600</v>
+      </c>
+      <c r="I24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>400</v>
       </c>
       <c r="R24" s="3">
         <v>400</v>
       </c>
       <c r="S24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T24" s="3">
         <v>300</v>
@@ -2188,43 +2234,46 @@
         <v>300</v>
       </c>
       <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3">
         <v>600</v>
-      </c>
-      <c r="W24" s="3">
-        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1400</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,49 +2367,52 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E26" s="3">
         <v>1600</v>
       </c>
       <c r="F26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1200</v>
-      </c>
-      <c r="P26" s="3">
-        <v>1000</v>
       </c>
       <c r="Q26" s="3">
         <v>1000</v>
@@ -2369,22 +2421,22 @@
         <v>1000</v>
       </c>
       <c r="S26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T26" s="3">
         <v>800</v>
       </c>
       <c r="U26" s="3">
+        <v>800</v>
+      </c>
+      <c r="V26" s="3">
         <v>1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
-      </c>
-      <c r="X26" s="3">
-        <v>800</v>
       </c>
       <c r="Y26" s="3">
         <v>800</v>
@@ -2393,13 +2445,13 @@
         <v>800</v>
       </c>
       <c r="AA26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB26" s="3">
         <v>600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>100</v>
       </c>
       <c r="AD26" s="3">
         <v>100</v>
@@ -2408,54 +2460,57 @@
         <v>100</v>
       </c>
       <c r="AF26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E27" s="3">
         <v>1600</v>
       </c>
       <c r="F27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1200</v>
-      </c>
-      <c r="P27" s="3">
-        <v>1000</v>
       </c>
       <c r="Q27" s="3">
         <v>1000</v>
@@ -2464,22 +2519,22 @@
         <v>1000</v>
       </c>
       <c r="S27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T27" s="3">
         <v>800</v>
       </c>
       <c r="U27" s="3">
+        <v>800</v>
+      </c>
+      <c r="V27" s="3">
         <v>1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
-      </c>
-      <c r="X27" s="3">
-        <v>800</v>
       </c>
       <c r="Y27" s="3">
         <v>800</v>
@@ -2488,13 +2543,13 @@
         <v>800</v>
       </c>
       <c r="AA27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>100</v>
       </c>
       <c r="AD27" s="3">
         <v>100</v>
@@ -2503,13 +2558,16 @@
         <v>100</v>
       </c>
       <c r="AF27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2662,8 +2723,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2680,8 +2741,8 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2897,64 +2967,64 @@
         <v>2900</v>
       </c>
       <c r="E32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2500</v>
       </c>
       <c r="I32" s="3">
         <v>2500</v>
       </c>
       <c r="J32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K32" s="3">
         <v>2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2200</v>
       </c>
       <c r="M32" s="3">
         <v>2200</v>
       </c>
       <c r="N32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>2000</v>
       </c>
       <c r="S32" s="3">
         <v>2000</v>
       </c>
       <c r="T32" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="U32" s="3">
         <v>1900</v>
       </c>
       <c r="V32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W32" s="3">
         <v>3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>2000</v>
       </c>
       <c r="Y32" s="3">
         <v>2000</v>
@@ -2966,66 +3036,69 @@
         <v>2000</v>
       </c>
       <c r="AB32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E33" s="3">
         <v>1600</v>
       </c>
       <c r="F33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1200</v>
-      </c>
-      <c r="P33" s="3">
-        <v>1000</v>
       </c>
       <c r="Q33" s="3">
         <v>1000</v>
@@ -3034,22 +3107,22 @@
         <v>1000</v>
       </c>
       <c r="S33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T33" s="3">
         <v>800</v>
       </c>
       <c r="U33" s="3">
+        <v>800</v>
+      </c>
+      <c r="V33" s="3">
         <v>1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
-      </c>
-      <c r="X33" s="3">
-        <v>800</v>
       </c>
       <c r="Y33" s="3">
         <v>800</v>
@@ -3058,13 +3131,13 @@
         <v>800</v>
       </c>
       <c r="AA33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>100</v>
       </c>
       <c r="AD33" s="3">
         <v>100</v>
@@ -3073,13 +3146,16 @@
         <v>100</v>
       </c>
       <c r="AF33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,49 +3249,52 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E35" s="3">
         <v>1600</v>
       </c>
       <c r="F35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1200</v>
-      </c>
-      <c r="P35" s="3">
-        <v>1000</v>
       </c>
       <c r="Q35" s="3">
         <v>1000</v>
@@ -3224,22 +3303,22 @@
         <v>1000</v>
       </c>
       <c r="S35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T35" s="3">
         <v>800</v>
       </c>
       <c r="U35" s="3">
+        <v>800</v>
+      </c>
+      <c r="V35" s="3">
         <v>1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
-      </c>
-      <c r="X35" s="3">
-        <v>800</v>
       </c>
       <c r="Y35" s="3">
         <v>800</v>
@@ -3248,13 +3327,13 @@
         <v>800</v>
       </c>
       <c r="AA35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>100</v>
       </c>
       <c r="AD35" s="3">
         <v>100</v>
@@ -3263,113 +3342,119 @@
         <v>100</v>
       </c>
       <c r="AF35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E41" s="3">
         <v>79000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>57300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>60900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>42200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>25600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>120400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>162500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>20700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3559,51 +3649,51 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M42" s="3">
         <v>48800</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P42" s="3">
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3">
         <v>49400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3">
         <v>17800</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3">
         <v>16100</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3622,14 +3712,17 @@
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>8300</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3913,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,8 +4110,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4129,60 +4237,60 @@
       <c r="J48" s="3">
         <v>0</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>9200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>9400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>8700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>7500</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>62300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>57400</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4192,19 +4300,22 @@
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>6700</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E49" s="3">
         <v>1700</v>
@@ -4213,7 +4324,7 @@
         <v>1700</v>
       </c>
       <c r="G49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="H49" s="3">
         <v>1800</v>
@@ -4222,22 +4333,22 @@
         <v>1800</v>
       </c>
       <c r="J49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="K49" s="3">
         <v>1900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M49" s="3">
-        <v>2000</v>
+      <c r="L49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N49" s="3">
         <v>2000</v>
       </c>
       <c r="O49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="P49" s="3">
         <v>2100</v>
@@ -4246,7 +4357,7 @@
         <v>2100</v>
       </c>
       <c r="R49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="S49" s="3">
         <v>2200</v>
@@ -4255,7 +4366,7 @@
         <v>2200</v>
       </c>
       <c r="U49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="V49" s="3">
         <v>2300</v>
@@ -4264,23 +4375,23 @@
         <v>2300</v>
       </c>
       <c r="X49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="Y49" s="3">
         <v>2400</v>
       </c>
       <c r="Z49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA49" s="3">
         <v>66100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>56300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2600</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4509,60 +4629,60 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>5900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2500</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4572,14 +4692,17 @@
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>3400</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>539500</v>
+      </c>
+      <c r="E54" s="3">
         <v>541600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>513300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>510600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>500200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>471600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>473800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>460300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>457900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>420700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>423300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>418300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>406300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>402200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>414800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>377200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>352600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>360000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>368700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>353300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>345000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>354000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2481700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2299400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>356000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>333700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>227900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>223900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>219500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4933,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,8 +5162,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5054,39 +5191,39 @@
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>3000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5102,8 +5239,8 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -5123,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,28 +5358,31 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>11000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>1500</v>
@@ -5248,7 +5391,7 @@
         <v>1500</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5260,11 +5403,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5272,11 +5415,11 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>2500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5284,20 +5427,20 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2500</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>75200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10300</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5313,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,8 +5848,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5731,48 +5889,48 @@
       <c r="N66" s="3">
         <v>0</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q66" s="3">
         <v>363500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>314900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>311200</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>2195900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2040900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5782,14 +5940,17 @@
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>199700</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,8 +6374,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6229,51 +6403,51 @@
       <c r="J72" s="3">
         <v>0</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="K72" s="3">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>35200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3">
         <v>30800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>27500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>24500</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6292,14 +6466,17 @@
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>21900</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E76" s="3">
         <v>53600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43800</v>
-      </c>
-      <c r="O76" s="3">
-        <v>42800</v>
       </c>
       <c r="P76" s="3">
         <v>42800</v>
       </c>
       <c r="Q76" s="3">
+        <v>42800</v>
+      </c>
+      <c r="R76" s="3">
         <v>42700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>41700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>40500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>37700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>36800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>33800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>32700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>285800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>258500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>31100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,149 +6962,155 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E81" s="3">
         <v>1600</v>
       </c>
       <c r="F81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1200</v>
-      </c>
-      <c r="P81" s="3">
-        <v>1000</v>
       </c>
       <c r="Q81" s="3">
         <v>1000</v>
@@ -6924,22 +7119,22 @@
         <v>1000</v>
       </c>
       <c r="S81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="T81" s="3">
         <v>800</v>
       </c>
       <c r="U81" s="3">
+        <v>800</v>
+      </c>
+      <c r="V81" s="3">
         <v>1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
-      </c>
-      <c r="X81" s="3">
-        <v>800</v>
       </c>
       <c r="Y81" s="3">
         <v>800</v>
@@ -6948,13 +7143,13 @@
         <v>800</v>
       </c>
       <c r="AA81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>100</v>
       </c>
       <c r="AD81" s="3">
         <v>100</v>
@@ -6963,13 +7158,16 @@
         <v>100</v>
       </c>
       <c r="AF81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,8 +7787,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7668,8 +7885,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8593,8 +8839,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,8 +8937,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8781,6 +9033,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,245 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8100</v>
+        <v>5700</v>
       </c>
       <c r="E8" s="3">
-        <v>7700</v>
+        <v>5600</v>
       </c>
       <c r="F8" s="3">
-        <v>7400</v>
+        <v>5500</v>
       </c>
       <c r="G8" s="3">
-        <v>7100</v>
+        <v>5600</v>
       </c>
       <c r="H8" s="3">
-        <v>6000</v>
+        <v>5600</v>
       </c>
       <c r="I8" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="J8" s="3">
         <v>5100</v>
       </c>
       <c r="K8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M8" s="3">
         <v>4600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3900</v>
-      </c>
-      <c r="R8" s="3">
-        <v>4100</v>
-      </c>
-      <c r="S8" s="3">
-        <v>4200</v>
       </c>
       <c r="T8" s="3">
         <v>4100</v>
       </c>
       <c r="U8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V8" s="3">
         <v>4100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="X8" s="3">
         <v>4300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>8400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>1800</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>1800</v>
       </c>
       <c r="AH8" s="3">
         <v>1800</v>
       </c>
+      <c r="AI8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>1800</v>
+      </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,31 +1005,37 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1089,8 +1109,14 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1151,10 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1251,14 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,31 +1355,37 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1419,8 +1459,14 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1434,13 +1480,13 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1475,11 +1521,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
@@ -1493,18 +1539,18 @@
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>-200</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1517,8 +1563,14 @@
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1602,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="E17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="F17" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1100</v>
       </c>
       <c r="V17" s="3">
         <v>1000</v>
       </c>
       <c r="W17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y17" s="3">
         <v>2400</v>
-      </c>
-      <c r="X17" s="3">
-        <v>800</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>800</v>
       </c>
       <c r="Z17" s="3">
         <v>800</v>
       </c>
       <c r="AA17" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC17" s="3">
         <v>700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5100</v>
+        <v>2100</v>
       </c>
       <c r="E18" s="3">
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="F18" s="3">
-        <v>5100</v>
+        <v>2200</v>
       </c>
       <c r="G18" s="3">
-        <v>5200</v>
+        <v>2100</v>
       </c>
       <c r="H18" s="3">
-        <v>4700</v>
+        <v>2100</v>
       </c>
       <c r="I18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>6000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>3000</v>
       </c>
       <c r="AA18" s="3">
         <v>3000</v>
       </c>
       <c r="AB18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AD18" s="3">
         <v>2800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>2300</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>1400</v>
       </c>
       <c r="AG18" s="3">
         <v>1500</v>
       </c>
       <c r="AH18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1500</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>1500</v>
+      </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,52 +1848,54 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2300</v>
       </c>
       <c r="M20" s="3">
         <v>-2200</v>
       </c>
       <c r="N20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-2000</v>
       </c>
       <c r="R20" s="3">
         <v>-1900</v>
@@ -1836,25 +1904,25 @@
         <v>-2000</v>
       </c>
       <c r="T20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-2000</v>
       </c>
       <c r="AA20" s="3">
         <v>-2000</v>
@@ -1863,48 +1931,54 @@
         <v>-2000</v>
       </c>
       <c r="AC20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1978,31 +2052,37 @@
       <c r="AH21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2076,106 +2156,118 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G23" s="3">
         <v>2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1900</v>
       </c>
       <c r="K23" s="3">
         <v>1900</v>
       </c>
       <c r="L23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1100</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>2300</v>
       </c>
       <c r="X23" s="3">
         <v>1300</v>
       </c>
       <c r="Y23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>600</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>200</v>
       </c>
       <c r="AF23" s="3">
         <v>100</v>
       </c>
       <c r="AG23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2186,67 +2278,67 @@
         <v>500</v>
       </c>
       <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>500</v>
+      </c>
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>500</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N24" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>400</v>
       </c>
       <c r="P24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>400</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
       <c r="W24" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z24" s="3">
         <v>300</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>200</v>
       </c>
       <c r="AA24" s="3">
         <v>300</v>
@@ -2255,25 +2347,31 @@
         <v>200</v>
       </c>
       <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2468,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E26" s="3">
         <v>1600</v>
       </c>
       <c r="F26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1000</v>
       </c>
       <c r="M26" s="3">
         <v>1400</v>
       </c>
       <c r="N26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P26" s="3">
         <v>1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>1000</v>
       </c>
       <c r="S26" s="3">
         <v>1000</v>
       </c>
       <c r="T26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
-      </c>
-      <c r="V26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>1800</v>
       </c>
       <c r="X26" s="3">
         <v>1000</v>
       </c>
       <c r="Y26" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="Z26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AA26" s="3">
         <v>800</v>
       </c>
       <c r="AB26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD26" s="3">
         <v>600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>100</v>
       </c>
       <c r="AF26" s="3">
         <v>100</v>
       </c>
       <c r="AG26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E27" s="3">
         <v>1600</v>
       </c>
       <c r="F27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1000</v>
       </c>
       <c r="M27" s="3">
         <v>1400</v>
       </c>
       <c r="N27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>1000</v>
       </c>
       <c r="S27" s="3">
         <v>1000</v>
       </c>
       <c r="T27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
-      </c>
-      <c r="V27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>1800</v>
       </c>
       <c r="X27" s="3">
         <v>1000</v>
       </c>
       <c r="Y27" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="Z27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AA27" s="3">
         <v>800</v>
       </c>
       <c r="AB27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>100</v>
       </c>
       <c r="AF27" s="3">
         <v>100</v>
       </c>
       <c r="AG27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI27" s="3">
         <v>700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2780,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,11 +2848,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2744,11 +2866,11 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2762,8 +2884,14 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2988,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,52 +3092,58 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2300</v>
       </c>
       <c r="M32" s="3">
         <v>2200</v>
       </c>
       <c r="N32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>2100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>2000</v>
       </c>
       <c r="R32" s="3">
         <v>1900</v>
@@ -3012,25 +3152,25 @@
         <v>2000</v>
       </c>
       <c r="T32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W32" s="3">
         <v>1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>2000</v>
       </c>
       <c r="AA32" s="3">
         <v>2000</v>
@@ -3039,123 +3179,135 @@
         <v>2000</v>
       </c>
       <c r="AC32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>2200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E33" s="3">
         <v>1600</v>
       </c>
       <c r="F33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1000</v>
       </c>
       <c r="M33" s="3">
         <v>1400</v>
       </c>
       <c r="N33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R33" s="3">
-        <v>1000</v>
       </c>
       <c r="S33" s="3">
         <v>1000</v>
       </c>
       <c r="T33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
-      </c>
-      <c r="V33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>1800</v>
       </c>
       <c r="X33" s="3">
         <v>1000</v>
       </c>
       <c r="Y33" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="Z33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AA33" s="3">
         <v>800</v>
       </c>
       <c r="AB33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>100</v>
       </c>
       <c r="AF33" s="3">
         <v>100</v>
       </c>
       <c r="AG33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI33" s="3">
         <v>700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3404,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E35" s="3">
         <v>1600</v>
       </c>
       <c r="F35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1000</v>
       </c>
       <c r="M35" s="3">
         <v>1400</v>
       </c>
       <c r="N35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R35" s="3">
-        <v>1000</v>
       </c>
       <c r="S35" s="3">
         <v>1000</v>
       </c>
       <c r="T35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
-      </c>
-      <c r="V35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>1800</v>
       </c>
       <c r="X35" s="3">
         <v>1000</v>
       </c>
       <c r="Y35" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="Z35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AA35" s="3">
         <v>800</v>
       </c>
       <c r="AB35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>100</v>
       </c>
       <c r="AF35" s="3">
         <v>100</v>
       </c>
       <c r="AG35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI35" s="3">
         <v>700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3659,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3697,114 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
+        <v>42800</v>
+      </c>
+      <c r="F41" s="3">
         <v>83000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>79000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>60700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>38700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>40800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>36000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>37300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>55600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>13400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>33300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>57300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>39800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>16400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>60900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>57300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>42200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>20200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>19000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>6000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>25600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>120400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>162500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>20700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>20300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>12400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>5800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>4700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3652,54 +3832,54 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="3">
         <v>48800</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3">
         <v>49400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
         <v>17800</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3">
         <v>16100</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3715,37 +3895,43 @@
       <c r="AF42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="3">
         <v>8300</v>
       </c>
-      <c r="AH42" s="3" t="s">
+      <c r="AJ42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3819,31 +4005,37 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3917,31 +4109,37 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4015,31 +4213,37 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>0</v>
+      <c r="D46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>42800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>83000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>60700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>38700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>40800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4113,31 +4317,37 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4211,193 +4421,205 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
+      <c r="L48" s="3">
+        <v>0</v>
       </c>
       <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>9200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>9400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>8700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>7500</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>62300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>57400</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>6700</v>
       </c>
-      <c r="AH48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>1600</v>
       </c>
-      <c r="E49" s="3">
-        <v>1700</v>
-      </c>
       <c r="F49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G49" s="3">
         <v>1700</v>
       </c>
       <c r="H49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="I49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="J49" s="3">
         <v>1800</v>
       </c>
       <c r="K49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M49" s="3">
         <v>1900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P49" s="3">
         <v>2000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>2100</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>2100</v>
       </c>
       <c r="R49" s="3">
         <v>2100</v>
       </c>
       <c r="S49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="T49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="U49" s="3">
         <v>2200</v>
       </c>
       <c r="V49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="W49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="X49" s="3">
         <v>2300</v>
       </c>
       <c r="Y49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA49" s="3">
         <v>2400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>66100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>56300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2600</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4407,8 +4629,14 @@
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4733,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4837,118 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>29700</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>5900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2500</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>3400</v>
       </c>
-      <c r="AH52" s="3" t="s">
+      <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +5045,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3">
+        <v>516800</v>
+      </c>
+      <c r="F54" s="3">
         <v>539500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>541600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>513300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>510600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>500200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>471600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>473800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>460300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>457900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P54" s="3">
         <v>420700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>423300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>418300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>406300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>402200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>414800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>377200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>352600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>360000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>368700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>353300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>345000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>354000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2481700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2299400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>356000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>333700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>227900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>223900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>219500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5191,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,31 +5229,33 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>455000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>478000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>472000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>444400</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>444500</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>434700</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5067,8 +5329,14 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5076,22 +5344,22 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5165,71 +5433,77 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>2700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>2400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>3000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5242,11 +5516,11 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5263,31 +5537,37 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>456600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>479400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>472800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>445200</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>445200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>435700</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5361,8 +5641,14 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5370,34 +5656,34 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>11000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1500</v>
-      </c>
       <c r="K61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>1500</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -5406,47 +5692,47 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>2500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>2500</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>75200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>10300</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5459,31 +5745,37 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5557,8 +5849,14 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5953,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +6057,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,31 +6161,37 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>0</v>
+      <c r="D66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E66" s="3">
-        <v>0</v>
+        <v>460700</v>
       </c>
       <c r="F66" s="3">
-        <v>0</v>
+        <v>484300</v>
       </c>
       <c r="G66" s="3">
-        <v>0</v>
+        <v>488000</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
+        <v>462200</v>
       </c>
       <c r="I66" s="3">
-        <v>0</v>
+        <v>460300</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>450800</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>
@@ -5892,65 +6208,71 @@
       <c r="O66" s="3">
         <v>0</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
+      <c r="P66" s="3">
+        <v>0</v>
       </c>
       <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>363500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>314900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>311200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>2195900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2040900</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>199700</v>
       </c>
-      <c r="AH66" s="3" t="s">
+      <c r="AJ66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6307,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6407,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6511,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6615,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,83 +6719,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
+      <c r="L72" s="3">
+        <v>0</v>
       </c>
       <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O72" s="3">
         <v>35200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>30800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>27500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>24500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6469,14 +6817,20 @@
       <c r="AF72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>21900</v>
       </c>
-      <c r="AH72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6927,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +7031,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +7135,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F76" s="3">
         <v>55200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>53600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>51100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>50300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>49400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>47600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>46300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>45100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>43900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>44200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>45000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>43800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>42800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>42800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>42700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>41700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>40500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>37700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>36800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>35800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>34500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>33800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>32700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>285800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>258500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>31100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>32000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>20300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>20000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>19800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7343,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="E81" s="3">
         <v>1600</v>
       </c>
       <c r="F81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1000</v>
       </c>
       <c r="M81" s="3">
         <v>1400</v>
       </c>
       <c r="N81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R81" s="3">
-        <v>1000</v>
       </c>
       <c r="S81" s="3">
         <v>1000</v>
       </c>
       <c r="T81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
-      </c>
-      <c r="V81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>1800</v>
       </c>
       <c r="X81" s="3">
         <v>1000</v>
       </c>
       <c r="Y81" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="Z81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AA81" s="3">
         <v>800</v>
       </c>
       <c r="AB81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>100</v>
       </c>
       <c r="AF81" s="3">
         <v>100</v>
       </c>
       <c r="AG81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI81" s="3">
         <v>700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,31 +7598,33 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7300,8 +7698,14 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7802,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7906,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +8010,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +8114,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,31 +8218,37 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7888,8 +8322,14 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,31 +8364,33 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8022,8 +8464,14 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8568,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,31 +8672,37 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8316,8 +8776,14 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8818,33 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8918,14 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +9022,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +9126,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,31 +9230,37 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8842,31 +9334,37 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8940,31 +9438,37 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9036,6 +9540,12 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,250 +656,253 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E8" s="3">
         <v>5700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5600</v>
       </c>
       <c r="H8" s="3">
         <v>5600</v>
       </c>
       <c r="I8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J8" s="3">
         <v>5700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>4100</v>
       </c>
       <c r="W8" s="3">
         <v>4100</v>
       </c>
       <c r="X8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>4300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3900</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>3800</v>
       </c>
       <c r="AB8" s="3">
         <v>3800</v>
       </c>
       <c r="AC8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>1800</v>
       </c>
       <c r="AI8" s="3">
         <v>1800</v>
@@ -907,8 +910,11 @@
       <c r="AJ8" s="3">
         <v>1800</v>
       </c>
+      <c r="AK8" s="3">
+        <v>1800</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1011,35 +1017,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E10" s="3">
         <v>5700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>5600</v>
       </c>
       <c r="H10" s="3">
         <v>5600</v>
       </c>
       <c r="I10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J10" s="3">
         <v>5700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1465,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1480,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1489,7 +1511,7 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1527,8 +1549,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1545,15 +1567,15 @@
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-200</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,79 +1629,80 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3500</v>
       </c>
       <c r="H17" s="3">
         <v>3500</v>
       </c>
       <c r="I17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>500</v>
       </c>
       <c r="N17" s="3">
         <v>500</v>
       </c>
       <c r="O17" s="3">
+        <v>500</v>
+      </c>
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>800</v>
       </c>
       <c r="U17" s="3">
         <v>800</v>
       </c>
       <c r="V17" s="3">
+        <v>800</v>
+      </c>
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2400</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>800</v>
       </c>
       <c r="AA17" s="3">
         <v>800</v>
@@ -1685,105 +1711,108 @@
         <v>800</v>
       </c>
       <c r="AC17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AD17" s="3">
         <v>700</v>
       </c>
       <c r="AE17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AF17" s="3">
         <v>500</v>
       </c>
       <c r="AG17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AH17" s="3">
         <v>400</v>
       </c>
       <c r="AI17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AJ17" s="3">
         <v>300</v>
       </c>
+      <c r="AK17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E18" s="3">
         <v>2100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2200</v>
       </c>
       <c r="F18" s="3">
         <v>2200</v>
       </c>
       <c r="G18" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="H18" s="3">
         <v>2100</v>
       </c>
       <c r="I18" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="J18" s="3">
         <v>2400</v>
       </c>
       <c r="K18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L18" s="3">
         <v>4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3600</v>
-      </c>
-      <c r="O18" s="3">
-        <v>4000</v>
       </c>
       <c r="P18" s="3">
         <v>4000</v>
       </c>
       <c r="Q18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R18" s="3">
         <v>3700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>3000</v>
       </c>
       <c r="AB18" s="3">
         <v>3000</v>
@@ -1792,28 +1821,31 @@
         <v>3000</v>
       </c>
       <c r="AD18" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AE18" s="3">
         <v>2800</v>
       </c>
       <c r="AF18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AG18" s="3">
         <v>2300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>1500</v>
       </c>
       <c r="AJ18" s="3">
         <v>1500</v>
       </c>
+      <c r="AK18" s="3">
+        <v>1500</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,56 +1909,56 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
-        <v>-2500</v>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L20" s="3">
         <v>-2500</v>
       </c>
       <c r="M20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-2200</v>
       </c>
       <c r="P20" s="3">
         <v>-2200</v>
       </c>
       <c r="Q20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1900</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-2000</v>
       </c>
       <c r="V20" s="3">
         <v>-2000</v>
       </c>
       <c r="W20" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="X20" s="3">
         <v>-1900</v>
       </c>
       <c r="Y20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-2000</v>
       </c>
       <c r="AB20" s="3">
         <v>-2000</v>
@@ -1937,52 +1970,55 @@
         <v>-2000</v>
       </c>
       <c r="AE20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E21" s="3">
         <v>2100</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2200</v>
       </c>
       <c r="F21" s="3">
         <v>2200</v>
       </c>
       <c r="G21" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="H21" s="3">
         <v>2300</v>
       </c>
       <c r="I21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J21" s="3">
         <v>2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2058,8 +2094,11 @@
       <c r="AJ21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,34 +2201,37 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2200</v>
       </c>
       <c r="F23" s="3">
         <v>2200</v>
       </c>
       <c r="G23" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="H23" s="3">
         <v>2100</v>
       </c>
       <c r="I23" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="J23" s="3">
         <v>2400</v>
       </c>
       <c r="K23" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="L23" s="3">
         <v>1900</v>
@@ -2198,76 +2240,79 @@
         <v>1900</v>
       </c>
       <c r="N23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O23" s="3">
         <v>1400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>1800</v>
       </c>
       <c r="P23" s="3">
         <v>1800</v>
       </c>
       <c r="Q23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R23" s="3">
         <v>1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1200</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1400</v>
       </c>
       <c r="U23" s="3">
         <v>1400</v>
       </c>
       <c r="V23" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="W23" s="3">
         <v>1100</v>
       </c>
       <c r="X23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>1100</v>
       </c>
       <c r="AB23" s="3">
         <v>1100</v>
       </c>
       <c r="AC23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2284,49 +2329,49 @@
         <v>500</v>
       </c>
       <c r="H24" s="3">
+        <v>500</v>
+      </c>
+      <c r="I24" s="3">
         <v>400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>600</v>
       </c>
       <c r="J24" s="3">
         <v>600</v>
       </c>
       <c r="K24" s="3">
+        <v>600</v>
+      </c>
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>400</v>
       </c>
       <c r="U24" s="3">
         <v>400</v>
       </c>
       <c r="V24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W24" s="3">
         <v>300</v>
@@ -2335,43 +2380,46 @@
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>600</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>300</v>
       </c>
       <c r="AA24" s="3">
         <v>300</v>
       </c>
       <c r="AB24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,58 +2522,61 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E26" s="3">
         <v>1600</v>
       </c>
       <c r="F26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G26" s="3">
         <v>1700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1600</v>
       </c>
       <c r="H26" s="3">
         <v>1600</v>
       </c>
       <c r="I26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
-      </c>
-      <c r="S26" s="3">
-        <v>1000</v>
       </c>
       <c r="T26" s="3">
         <v>1000</v>
@@ -2534,22 +2585,22 @@
         <v>1000</v>
       </c>
       <c r="V26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W26" s="3">
         <v>800</v>
       </c>
       <c r="X26" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>800</v>
       </c>
       <c r="AB26" s="3">
         <v>800</v>
@@ -2558,13 +2609,13 @@
         <v>800</v>
       </c>
       <c r="AD26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE26" s="3">
         <v>600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>100</v>
       </c>
       <c r="AG26" s="3">
         <v>100</v>
@@ -2573,63 +2624,66 @@
         <v>100</v>
       </c>
       <c r="AI26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E27" s="3">
         <v>1600</v>
       </c>
       <c r="F27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G27" s="3">
         <v>1700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1600</v>
       </c>
       <c r="H27" s="3">
         <v>1600</v>
       </c>
       <c r="I27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1000</v>
       </c>
       <c r="T27" s="3">
         <v>1000</v>
@@ -2638,22 +2692,22 @@
         <v>1000</v>
       </c>
       <c r="V27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W27" s="3">
         <v>800</v>
       </c>
       <c r="X27" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>800</v>
       </c>
       <c r="AB27" s="3">
         <v>800</v>
@@ -2662,13 +2716,13 @@
         <v>800</v>
       </c>
       <c r="AD27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>100</v>
       </c>
       <c r="AG27" s="3">
         <v>100</v>
@@ -2677,13 +2731,16 @@
         <v>100</v>
       </c>
       <c r="AI27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,8 +2914,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2872,8 +2932,8 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,56 +3193,56 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
-        <v>2500</v>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <v>2500</v>
       </c>
       <c r="M32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N32" s="3">
         <v>2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>2200</v>
       </c>
       <c r="P32" s="3">
         <v>2200</v>
       </c>
       <c r="Q32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1900</v>
-      </c>
-      <c r="U32" s="3">
-        <v>2000</v>
       </c>
       <c r="V32" s="3">
         <v>2000</v>
       </c>
       <c r="W32" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="X32" s="3">
         <v>1900</v>
       </c>
       <c r="Y32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z32" s="3">
         <v>3700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>2000</v>
       </c>
       <c r="AB32" s="3">
         <v>2000</v>
@@ -3185,75 +3254,78 @@
         <v>2000</v>
       </c>
       <c r="AE32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>2200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E33" s="3">
         <v>1600</v>
       </c>
       <c r="F33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G33" s="3">
         <v>1700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1600</v>
       </c>
       <c r="H33" s="3">
         <v>1600</v>
       </c>
       <c r="I33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
-      </c>
-      <c r="S33" s="3">
-        <v>1000</v>
       </c>
       <c r="T33" s="3">
         <v>1000</v>
@@ -3262,22 +3334,22 @@
         <v>1000</v>
       </c>
       <c r="V33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W33" s="3">
         <v>800</v>
       </c>
       <c r="X33" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>800</v>
       </c>
       <c r="AB33" s="3">
         <v>800</v>
@@ -3286,13 +3358,13 @@
         <v>800</v>
       </c>
       <c r="AD33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>100</v>
       </c>
       <c r="AG33" s="3">
         <v>100</v>
@@ -3301,13 +3373,16 @@
         <v>100</v>
       </c>
       <c r="AI33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,58 +3485,61 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E35" s="3">
         <v>1600</v>
       </c>
       <c r="F35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G35" s="3">
         <v>1700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1600</v>
       </c>
       <c r="H35" s="3">
         <v>1600</v>
       </c>
       <c r="I35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
-      </c>
-      <c r="S35" s="3">
-        <v>1000</v>
       </c>
       <c r="T35" s="3">
         <v>1000</v>
@@ -3470,22 +3548,22 @@
         <v>1000</v>
       </c>
       <c r="V35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W35" s="3">
         <v>800</v>
       </c>
       <c r="X35" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>800</v>
       </c>
       <c r="AB35" s="3">
         <v>800</v>
@@ -3494,13 +3572,13 @@
         <v>800</v>
       </c>
       <c r="AD35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>100</v>
       </c>
       <c r="AG35" s="3">
         <v>100</v>
@@ -3509,122 +3587,128 @@
         <v>100</v>
       </c>
       <c r="AI35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3">
         <v>42800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>83000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>79000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>60700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>55600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>39800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>60900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>42200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>25600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>120400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>162500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3838,51 +3927,51 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P42" s="3">
         <v>48800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="3">
         <v>49400</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>17800</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>16100</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3901,14 +3990,17 @@
       <c r="AH42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AK42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3933,8 +4025,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,8 +4239,8 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4219,35 +4317,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
         <v>42800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>83000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>79000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>60700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,35 +4424,38 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
-        <v>13000</v>
+      <c r="D47" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
         <v>13000</v>
       </c>
       <c r="G47" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H47" s="3">
         <v>13100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4427,8 +4531,11 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4453,8 +4560,8 @@
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4462,60 +4569,60 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>9200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>9400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>8700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>7500</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>62300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>57400</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4525,28 +4632,31 @@
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ48" s="3" t="s">
+      <c r="AK48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>1600</v>
       </c>
       <c r="G49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="H49" s="3">
         <v>1700</v>
@@ -4555,7 +4665,7 @@
         <v>1700</v>
       </c>
       <c r="J49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="K49" s="3">
         <v>1800</v>
@@ -4564,22 +4674,22 @@
         <v>1800</v>
       </c>
       <c r="M49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="N49" s="3">
         <v>1900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3">
-        <v>2000</v>
+      <c r="O49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q49" s="3">
         <v>2000</v>
       </c>
       <c r="R49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="S49" s="3">
         <v>2100</v>
@@ -4588,7 +4698,7 @@
         <v>2100</v>
       </c>
       <c r="U49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="V49" s="3">
         <v>2200</v>
@@ -4597,7 +4707,7 @@
         <v>2200</v>
       </c>
       <c r="X49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="Y49" s="3">
         <v>2300</v>
@@ -4606,23 +4716,23 @@
         <v>2300</v>
       </c>
       <c r="AA49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="AB49" s="3">
         <v>2400</v>
       </c>
       <c r="AC49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD49" s="3">
         <v>66100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>56300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2600</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,34 +4959,37 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>30000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>29300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>28800</v>
       </c>
       <c r="J52" s="3">
         <v>28800</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4878,60 +4997,60 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1100</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>5900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2500</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4941,14 +5060,17 @@
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ52" s="3" t="s">
+      <c r="AK52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3">
+        <v>537900</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3">
         <v>516800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>539500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>541600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>513300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>510600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>500200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>471600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>473800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>460300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>457900</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="3">
         <v>420700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>423300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>418300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>406300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>402200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>414800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>377200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>352600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>360000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>368700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>353300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>345000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>354000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2481700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2299400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>356000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>333700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>227900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>223900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>219500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,35 +5360,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3">
+        <v>472600</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>455000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>478000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>472000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>444400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>444500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>434700</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5335,22 +5465,25 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>800</v>
       </c>
       <c r="H58" s="3">
         <v>800</v>
@@ -5359,11 +5492,11 @@
         <v>800</v>
       </c>
       <c r="J58" s="3">
+        <v>800</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5439,8 +5572,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5465,8 +5601,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5474,39 +5610,39 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>2400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>3000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5522,8 +5658,8 @@
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5543,35 +5679,38 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3">
+        <v>473700</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
         <v>456600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>479400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>472800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>445200</v>
       </c>
       <c r="I60" s="3">
         <v>445200</v>
       </c>
       <c r="J60" s="3">
+        <v>445200</v>
+      </c>
+      <c r="K60" s="3">
         <v>435700</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5647,8 +5786,11 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5662,22 +5804,22 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>11000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>1500</v>
@@ -5686,7 +5828,7 @@
         <v>1500</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -5698,11 +5840,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>2500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5710,11 +5852,11 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>2500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5722,20 +5864,20 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>2500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>75200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10300</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5751,35 +5893,38 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>4200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4100</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,35 +6321,38 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3">
+        <v>478300</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3">
         <v>460700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>484300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>488000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>462200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>460300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>450800</v>
       </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
       <c r="L66" s="3">
         <v>0</v>
       </c>
@@ -6214,48 +6371,48 @@
       <c r="Q66" s="3">
         <v>0</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>363500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>314900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>311200</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>2195900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2040900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6265,14 +6422,17 @@
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>199700</v>
       </c>
-      <c r="AJ66" s="3" t="s">
+      <c r="AK66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6751,8 +6924,8 @@
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -6760,51 +6933,51 @@
       <c r="M72" s="3">
         <v>0</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>35200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>30800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>27500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>24500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6823,14 +6996,17 @@
       <c r="AH72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>56000</v>
+        <v>59600</v>
       </c>
       <c r="E76" s="3">
         <v>56000</v>
       </c>
       <c r="F76" s="3">
+        <v>56000</v>
+      </c>
+      <c r="G76" s="3">
         <v>55200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43800</v>
-      </c>
-      <c r="R76" s="3">
-        <v>42800</v>
       </c>
       <c r="S76" s="3">
         <v>42800</v>
       </c>
       <c r="T76" s="3">
+        <v>42800</v>
+      </c>
+      <c r="U76" s="3">
         <v>42700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>41700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>40500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>37700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>36800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>34500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>33800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>32700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>285800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>258500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>31100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,167 +7537,173 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E81" s="3">
         <v>1600</v>
       </c>
       <c r="F81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G81" s="3">
         <v>1700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1600</v>
       </c>
       <c r="H81" s="3">
         <v>1600</v>
       </c>
       <c r="I81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
-      </c>
-      <c r="S81" s="3">
-        <v>1000</v>
       </c>
       <c r="T81" s="3">
         <v>1000</v>
@@ -7518,22 +7712,22 @@
         <v>1000</v>
       </c>
       <c r="V81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W81" s="3">
         <v>800</v>
       </c>
       <c r="X81" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>800</v>
       </c>
       <c r="AB81" s="3">
         <v>800</v>
@@ -7542,13 +7736,13 @@
         <v>800</v>
       </c>
       <c r="AD81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>100</v>
       </c>
       <c r="AG81" s="3">
         <v>100</v>
@@ -7557,13 +7751,16 @@
         <v>100</v>
       </c>
       <c r="AI81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7626,8 +7824,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,8 +8437,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8250,8 +8466,8 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8328,8 +8544,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,8 +8612,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8704,8 +8933,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8782,8 +9011,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9478,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9262,8 +9507,8 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9340,8 +9585,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9470,8 +9721,8 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9546,6 +9797,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,256 +656,260 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E8" s="3">
         <v>5900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5600</v>
       </c>
       <c r="I8" s="3">
         <v>5600</v>
       </c>
       <c r="J8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K8" s="3">
         <v>5700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4200</v>
-      </c>
-      <c r="W8" s="3">
-        <v>4100</v>
       </c>
       <c r="X8" s="3">
         <v>4100</v>
       </c>
       <c r="Y8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Z8" s="3">
         <v>4300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3900</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>3800</v>
       </c>
       <c r="AC8" s="3">
         <v>3800</v>
       </c>
       <c r="AD8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AE8" s="3">
         <v>3700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>1800</v>
       </c>
       <c r="AJ8" s="3">
         <v>1800</v>
@@ -913,8 +917,11 @@
       <c r="AK8" s="3">
         <v>1800</v>
       </c>
+      <c r="AL8" s="3">
+        <v>1800</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1020,38 +1027,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E10" s="3">
         <v>5900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>5600</v>
       </c>
       <c r="I10" s="3">
         <v>5600</v>
       </c>
       <c r="J10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K10" s="3">
         <v>5700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1429,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1487,8 +1507,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1505,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
@@ -1514,7 +1537,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1552,8 +1575,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>5</v>
@@ -1570,15 +1593,15 @@
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-200</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,82 +1656,83 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3500</v>
       </c>
       <c r="I17" s="3">
         <v>3500</v>
       </c>
       <c r="J17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>500</v>
       </c>
       <c r="O17" s="3">
         <v>500</v>
       </c>
       <c r="P17" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>800</v>
       </c>
       <c r="V17" s="3">
         <v>800</v>
       </c>
       <c r="W17" s="3">
+        <v>800</v>
+      </c>
+      <c r="X17" s="3">
         <v>1000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2400</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>800</v>
       </c>
       <c r="AB17" s="3">
         <v>800</v>
@@ -1714,108 +1741,111 @@
         <v>800</v>
       </c>
       <c r="AD17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AE17" s="3">
         <v>700</v>
       </c>
       <c r="AF17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AG17" s="3">
         <v>500</v>
       </c>
       <c r="AH17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AI17" s="3">
         <v>400</v>
       </c>
       <c r="AJ17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AK17" s="3">
         <v>300</v>
       </c>
+      <c r="AL17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2200</v>
       </c>
       <c r="G18" s="3">
         <v>2200</v>
       </c>
       <c r="H18" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I18" s="3">
         <v>2100</v>
       </c>
       <c r="J18" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="K18" s="3">
         <v>2400</v>
       </c>
       <c r="L18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M18" s="3">
         <v>4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>4000</v>
       </c>
       <c r="Q18" s="3">
         <v>4000</v>
       </c>
       <c r="R18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S18" s="3">
         <v>3700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>3000</v>
       </c>
       <c r="AC18" s="3">
         <v>3000</v>
@@ -1824,28 +1854,31 @@
         <v>3000</v>
       </c>
       <c r="AE18" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AF18" s="3">
         <v>2800</v>
       </c>
       <c r="AG18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AH18" s="3">
         <v>2300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>1500</v>
       </c>
       <c r="AK18" s="3">
         <v>1500</v>
       </c>
+      <c r="AL18" s="3">
+        <v>1500</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,56 +1946,56 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
-        <v>-2500</v>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M20" s="3">
         <v>-2500</v>
       </c>
       <c r="N20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-2200</v>
       </c>
       <c r="Q20" s="3">
         <v>-2200</v>
       </c>
       <c r="R20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-2000</v>
       </c>
       <c r="W20" s="3">
         <v>-2000</v>
       </c>
       <c r="X20" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="Y20" s="3">
         <v>-1900</v>
       </c>
       <c r="Z20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-2000</v>
       </c>
       <c r="AC20" s="3">
         <v>-2000</v>
@@ -1973,55 +2007,58 @@
         <v>-2000</v>
       </c>
       <c r="AF20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E21" s="3">
         <v>2200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2200</v>
       </c>
       <c r="G21" s="3">
         <v>2200</v>
       </c>
       <c r="H21" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="I21" s="3">
         <v>2300</v>
       </c>
       <c r="J21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K21" s="3">
         <v>2600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2097,8 +2134,11 @@
       <c r="AK21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,37 +2244,40 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2200</v>
       </c>
       <c r="G23" s="3">
         <v>2200</v>
       </c>
       <c r="H23" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I23" s="3">
         <v>2100</v>
       </c>
       <c r="J23" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="K23" s="3">
         <v>2400</v>
       </c>
       <c r="L23" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="M23" s="3">
         <v>1900</v>
@@ -2243,81 +2286,84 @@
         <v>1900</v>
       </c>
       <c r="O23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P23" s="3">
         <v>1400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1800</v>
       </c>
       <c r="Q23" s="3">
         <v>1800</v>
       </c>
       <c r="R23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S23" s="3">
         <v>1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1200</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1400</v>
       </c>
       <c r="V23" s="3">
         <v>1400</v>
       </c>
       <c r="W23" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="X23" s="3">
         <v>1100</v>
       </c>
       <c r="Y23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>1100</v>
       </c>
       <c r="AC23" s="3">
         <v>1100</v>
       </c>
       <c r="AD23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>1000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>100</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>0</v>
-      </c>
       <c r="AK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
         <v>500</v>
@@ -2332,49 +2378,49 @@
         <v>500</v>
       </c>
       <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>600</v>
       </c>
       <c r="K24" s="3">
         <v>600</v>
       </c>
       <c r="L24" s="3">
+        <v>600</v>
+      </c>
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>400</v>
       </c>
       <c r="V24" s="3">
         <v>400</v>
       </c>
       <c r="W24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
@@ -2383,43 +2429,46 @@
         <v>300</v>
       </c>
       <c r="Z24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA24" s="3">
         <v>600</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>300</v>
       </c>
       <c r="AB24" s="3">
         <v>300</v>
       </c>
       <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>-700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2574,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2534,52 +2586,52 @@
         <v>1700</v>
       </c>
       <c r="E26" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F26" s="3">
         <v>1600</v>
       </c>
       <c r="G26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H26" s="3">
         <v>1700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1600</v>
       </c>
       <c r="I26" s="3">
         <v>1600</v>
       </c>
       <c r="J26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1000</v>
       </c>
       <c r="U26" s="3">
         <v>1000</v>
@@ -2588,22 +2640,22 @@
         <v>1000</v>
       </c>
       <c r="W26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="X26" s="3">
         <v>800</v>
       </c>
       <c r="Y26" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>800</v>
       </c>
       <c r="AC26" s="3">
         <v>800</v>
@@ -2612,13 +2664,13 @@
         <v>800</v>
       </c>
       <c r="AE26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF26" s="3">
         <v>600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>100</v>
       </c>
       <c r="AH26" s="3">
         <v>100</v>
@@ -2627,13 +2679,16 @@
         <v>100</v>
       </c>
       <c r="AJ26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK26" s="3">
         <v>700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2641,52 +2696,52 @@
         <v>1700</v>
       </c>
       <c r="E27" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F27" s="3">
         <v>1600</v>
       </c>
       <c r="G27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H27" s="3">
         <v>1700</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1600</v>
       </c>
       <c r="I27" s="3">
         <v>1600</v>
       </c>
       <c r="J27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1000</v>
       </c>
       <c r="U27" s="3">
         <v>1000</v>
@@ -2695,22 +2750,22 @@
         <v>1000</v>
       </c>
       <c r="W27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="X27" s="3">
         <v>800</v>
       </c>
       <c r="Y27" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z27" s="3">
         <v>1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>800</v>
       </c>
       <c r="AC27" s="3">
         <v>800</v>
@@ -2719,13 +2774,13 @@
         <v>800</v>
       </c>
       <c r="AE27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>100</v>
       </c>
       <c r="AH27" s="3">
         <v>100</v>
@@ -2734,13 +2789,16 @@
         <v>100</v>
       </c>
       <c r="AJ27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK27" s="3">
         <v>700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2917,8 +2978,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2935,8 +2996,8 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,56 +3266,56 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
-        <v>2500</v>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M32" s="3">
         <v>2500</v>
       </c>
       <c r="N32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>2200</v>
       </c>
       <c r="Q32" s="3">
         <v>2200</v>
       </c>
       <c r="R32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1900</v>
-      </c>
-      <c r="V32" s="3">
-        <v>2000</v>
       </c>
       <c r="W32" s="3">
         <v>2000</v>
       </c>
       <c r="X32" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="Y32" s="3">
         <v>1900</v>
       </c>
       <c r="Z32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA32" s="3">
         <v>3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>2000</v>
       </c>
       <c r="AC32" s="3">
         <v>2000</v>
@@ -3257,25 +3327,28 @@
         <v>2000</v>
       </c>
       <c r="AF32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>2200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3283,52 +3356,52 @@
         <v>1700</v>
       </c>
       <c r="E33" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F33" s="3">
         <v>1600</v>
       </c>
       <c r="G33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H33" s="3">
         <v>1700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1600</v>
       </c>
       <c r="I33" s="3">
         <v>1600</v>
       </c>
       <c r="J33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1000</v>
       </c>
       <c r="U33" s="3">
         <v>1000</v>
@@ -3337,22 +3410,22 @@
         <v>1000</v>
       </c>
       <c r="W33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="X33" s="3">
         <v>800</v>
       </c>
       <c r="Y33" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z33" s="3">
         <v>1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>800</v>
       </c>
       <c r="AC33" s="3">
         <v>800</v>
@@ -3361,13 +3434,13 @@
         <v>800</v>
       </c>
       <c r="AE33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF33" s="3">
         <v>600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>100</v>
       </c>
       <c r="AH33" s="3">
         <v>100</v>
@@ -3376,13 +3449,16 @@
         <v>100</v>
       </c>
       <c r="AJ33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK33" s="3">
         <v>700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3564,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3497,52 +3576,52 @@
         <v>1700</v>
       </c>
       <c r="E35" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F35" s="3">
         <v>1600</v>
       </c>
       <c r="G35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H35" s="3">
         <v>1700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1600</v>
       </c>
       <c r="I35" s="3">
         <v>1600</v>
       </c>
       <c r="J35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1000</v>
       </c>
       <c r="U35" s="3">
         <v>1000</v>
@@ -3551,22 +3630,22 @@
         <v>1000</v>
       </c>
       <c r="W35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="X35" s="3">
         <v>800</v>
       </c>
       <c r="Y35" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z35" s="3">
         <v>1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>800</v>
       </c>
       <c r="AC35" s="3">
         <v>800</v>
@@ -3575,13 +3654,13 @@
         <v>800</v>
       </c>
       <c r="AE35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF35" s="3">
         <v>600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>100</v>
       </c>
       <c r="AH35" s="3">
         <v>100</v>
@@ -3590,125 +3669,131 @@
         <v>100</v>
       </c>
       <c r="AJ35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK35" s="3">
         <v>700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E41" s="3">
         <v>68600</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3">
         <v>42800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>79000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>60700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>37300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>55600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>33300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>60900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>57300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>42200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>20200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>19000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>25600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>120400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>162500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3930,51 +4020,51 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3">
         <v>48800</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3">
         <v>49400</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3">
         <v>17800</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>16100</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
@@ -3993,14 +4083,17 @@
       <c r="AI42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AJ42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK42" s="3">
         <v>8300</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AL42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4028,8 +4121,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,8 +4341,8 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4320,38 +4419,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E46" s="3">
         <v>68600</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3">
         <v>42800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>83000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>79000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>60700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4427,38 +4529,41 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E47" s="3">
         <v>13100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3">
-        <v>13000</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G47" s="3">
         <v>13000</v>
       </c>
       <c r="H47" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I47" s="3">
         <v>13100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4534,8 +4639,11 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4563,8 +4671,8 @@
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4572,60 +4680,60 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>9200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>9400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>8700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>7500</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>62300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>57400</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4635,14 +4743,17 @@
       <c r="AI48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>6700</v>
       </c>
-      <c r="AK48" s="3" t="s">
+      <c r="AL48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4650,16 +4761,16 @@
         <v>1500</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F49" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>1600</v>
       </c>
       <c r="H49" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I49" s="3">
         <v>1700</v>
@@ -4668,7 +4779,7 @@
         <v>1700</v>
       </c>
       <c r="K49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="L49" s="3">
         <v>1800</v>
@@ -4677,22 +4788,22 @@
         <v>1800</v>
       </c>
       <c r="N49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="O49" s="3">
         <v>1900</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>2000</v>
+      <c r="P49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R49" s="3">
         <v>2000</v>
       </c>
       <c r="S49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="T49" s="3">
         <v>2100</v>
@@ -4701,7 +4812,7 @@
         <v>2100</v>
       </c>
       <c r="V49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="W49" s="3">
         <v>2200</v>
@@ -4710,7 +4821,7 @@
         <v>2200</v>
       </c>
       <c r="Y49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="Z49" s="3">
         <v>2300</v>
@@ -4719,23 +4830,23 @@
         <v>2300</v>
       </c>
       <c r="AB49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="AC49" s="3">
         <v>2400</v>
       </c>
       <c r="AD49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE49" s="3">
         <v>66100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>56300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2600</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,37 +5079,40 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E52" s="3">
         <v>31100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3">
         <v>30000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>28800</v>
       </c>
       <c r="K52" s="3">
         <v>28800</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -5000,60 +5120,60 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>5900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2500</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5063,14 +5183,17 @@
       <c r="AI52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>3400</v>
       </c>
-      <c r="AK52" s="3" t="s">
+      <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>532400</v>
+      </c>
+      <c r="E54" s="3">
         <v>537900</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3">
         <v>516800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>539500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>541600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>513300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>510600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>500200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>471600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>473800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>460300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>457900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R54" s="3">
         <v>420700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>423300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>418300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>406300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>402200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>414800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>377200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>352600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>360000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>368700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>353300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>345000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>354000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2481700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2299400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>356000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>333700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>227900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>223900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>219500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,38 +5491,39 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>464100</v>
+      </c>
+      <c r="E57" s="3">
         <v>472600</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3">
         <v>455000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>478000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>472000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>444400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>444500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>434700</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5468,25 +5599,28 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>800</v>
       </c>
       <c r="I58" s="3">
         <v>800</v>
@@ -5495,11 +5629,11 @@
         <v>800</v>
       </c>
       <c r="K58" s="3">
+        <v>800</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5575,8 +5709,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5604,8 +5741,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5613,39 +5750,39 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>2400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>3000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5661,8 +5798,8 @@
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5682,38 +5819,41 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>465400</v>
+      </c>
+      <c r="E60" s="3">
         <v>473700</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3">
         <v>456600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>479400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>472800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>445200</v>
       </c>
       <c r="J60" s="3">
         <v>445200</v>
       </c>
       <c r="K60" s="3">
+        <v>445200</v>
+      </c>
+      <c r="L60" s="3">
         <v>435700</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5789,8 +5929,11 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5807,22 +5950,22 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>11000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>1500</v>
@@ -5831,7 +5974,7 @@
         <v>1500</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -5843,11 +5986,11 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>2500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5855,11 +5998,11 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>2500</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5867,20 +6010,20 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>2500</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>75200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10300</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5896,38 +6039,41 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4600</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3">
         <v>4200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,38 +6479,41 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E66" s="3">
         <v>478300</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3">
         <v>460700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>484300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>488000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>462200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>460300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>450800</v>
       </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
       <c r="M66" s="3">
         <v>0</v>
       </c>
@@ -6374,48 +6532,48 @@
       <c r="R66" s="3">
         <v>0</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="S66" s="3">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>363500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>314900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>311200</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>2195900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2040900</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6425,14 +6583,17 @@
       <c r="AI66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK66" s="3">
         <v>199700</v>
       </c>
-      <c r="AK66" s="3" t="s">
+      <c r="AL66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,8 +7069,11 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6927,8 +7101,8 @@
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
@@ -6936,51 +7110,51 @@
       <c r="N72" s="3">
         <v>0</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3">
         <v>35200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>30800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>27500</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>24500</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>5</v>
       </c>
@@ -6999,14 +7173,17 @@
       <c r="AI72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>21900</v>
       </c>
-      <c r="AK72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E76" s="3">
         <v>59600</v>
-      </c>
-      <c r="E76" s="3">
-        <v>56000</v>
       </c>
       <c r="F76" s="3">
         <v>56000</v>
       </c>
       <c r="G76" s="3">
+        <v>56000</v>
+      </c>
+      <c r="H76" s="3">
         <v>55200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>50300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>43800</v>
-      </c>
-      <c r="S76" s="3">
-        <v>42800</v>
       </c>
       <c r="T76" s="3">
         <v>42800</v>
       </c>
       <c r="U76" s="3">
+        <v>42800</v>
+      </c>
+      <c r="V76" s="3">
         <v>42700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>41700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>37700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>35800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>34500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>33800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>32700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>285800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>258500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>31100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7729,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7661,52 +7856,52 @@
         <v>1700</v>
       </c>
       <c r="E81" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F81" s="3">
         <v>1600</v>
       </c>
       <c r="G81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H81" s="3">
         <v>1700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1600</v>
       </c>
       <c r="I81" s="3">
         <v>1600</v>
       </c>
       <c r="J81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
-      </c>
-      <c r="T81" s="3">
-        <v>1000</v>
       </c>
       <c r="U81" s="3">
         <v>1000</v>
@@ -7715,22 +7910,22 @@
         <v>1000</v>
       </c>
       <c r="W81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="X81" s="3">
         <v>800</v>
       </c>
       <c r="Y81" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z81" s="3">
         <v>1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>800</v>
       </c>
       <c r="AC81" s="3">
         <v>800</v>
@@ -7739,13 +7934,13 @@
         <v>800</v>
       </c>
       <c r="AE81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF81" s="3">
         <v>600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>100</v>
       </c>
       <c r="AH81" s="3">
         <v>100</v>
@@ -7754,13 +7949,16 @@
         <v>100</v>
       </c>
       <c r="AJ81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK81" s="3">
         <v>700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7827,8 +8026,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,8 +8654,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8469,8 +8686,8 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -8547,8 +8764,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8615,8 +8836,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8936,8 +9166,8 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -9014,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9510,8 +9756,8 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9588,8 +9834,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,8 +9944,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9724,8 +9976,8 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -9800,6 +10052,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="92">
   <si>
     <t>FBSI</t>
   </si>
@@ -656,263 +656,267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>5800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L8" s="3">
         <v>5700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="M8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N8" s="3">
         <v>5600</v>
       </c>
-      <c r="H8" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K8" s="3">
-        <v>5700</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>5100</v>
       </c>
-      <c r="M8" s="3">
-        <v>5600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>5100</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>4100</v>
       </c>
       <c r="Y8" s="3">
         <v>4100</v>
       </c>
       <c r="Z8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>4300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3900</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>3800</v>
       </c>
       <c r="AD8" s="3">
         <v>3800</v>
       </c>
       <c r="AE8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AF8" s="3">
         <v>3700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1900</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>1800</v>
       </c>
       <c r="AK8" s="3">
         <v>1800</v>
@@ -920,8 +924,11 @@
       <c r="AL8" s="3">
         <v>1800</v>
       </c>
+      <c r="AM8" s="3">
+        <v>1800</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1030,41 +1037,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>5800</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L10" s="3">
         <v>5700</v>
       </c>
-      <c r="G10" s="3">
-        <v>5600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I10" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J10" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K10" s="3">
-        <v>5700</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1531,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1578,8 +1601,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>5</v>
@@ -1596,15 +1619,15 @@
       <c r="AD15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-200</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM15" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,85 +1683,86 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>500</v>
       </c>
       <c r="P17" s="3">
         <v>500</v>
       </c>
       <c r="Q17" s="3">
+        <v>500</v>
+      </c>
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>700</v>
-      </c>
-      <c r="V17" s="3">
-        <v>800</v>
       </c>
       <c r="W17" s="3">
         <v>800</v>
       </c>
       <c r="X17" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2400</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>800</v>
       </c>
       <c r="AC17" s="3">
         <v>800</v>
@@ -1744,111 +1771,114 @@
         <v>800</v>
       </c>
       <c r="AE17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AF17" s="3">
         <v>700</v>
       </c>
       <c r="AG17" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AH17" s="3">
         <v>500</v>
       </c>
       <c r="AI17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AJ17" s="3">
         <v>400</v>
       </c>
       <c r="AK17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AL17" s="3">
         <v>300</v>
       </c>
+      <c r="AM17" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>2100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2400</v>
       </c>
       <c r="L18" s="3">
         <v>2400</v>
       </c>
       <c r="M18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N18" s="3">
         <v>4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>4000</v>
       </c>
       <c r="R18" s="3">
         <v>4000</v>
       </c>
       <c r="S18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T18" s="3">
         <v>3700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3100</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>3000</v>
       </c>
       <c r="AD18" s="3">
         <v>3000</v>
@@ -1857,28 +1887,31 @@
         <v>3000</v>
       </c>
       <c r="AF18" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="AG18" s="3">
         <v>2800</v>
       </c>
       <c r="AH18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AI18" s="3">
         <v>2300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1400</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>1500</v>
       </c>
       <c r="AL18" s="3">
         <v>1500</v>
       </c>
+      <c r="AM18" s="3">
+        <v>1500</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,56 +1983,56 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
-        <v>-2500</v>
+      <c r="M20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N20" s="3">
         <v>-2500</v>
       </c>
       <c r="O20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-2200</v>
       </c>
       <c r="R20" s="3">
         <v>-2200</v>
       </c>
       <c r="S20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-2000</v>
       </c>
       <c r="X20" s="3">
         <v>-2000</v>
       </c>
       <c r="Y20" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="Z20" s="3">
         <v>-1900</v>
       </c>
       <c r="AA20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-2000</v>
       </c>
       <c r="AD20" s="3">
         <v>-2000</v>
@@ -2010,58 +2044,61 @@
         <v>-2000</v>
       </c>
       <c r="AG20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>2300</v>
       </c>
-      <c r="E21" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2137,8 +2174,11 @@
       <c r="AL21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,40 +2287,43 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>2300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>2100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>2400</v>
       </c>
       <c r="L23" s="3">
         <v>2400</v>
       </c>
       <c r="M23" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="N23" s="3">
         <v>1900</v>
@@ -2289,141 +2332,144 @@
         <v>1900</v>
       </c>
       <c r="P23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1800</v>
       </c>
       <c r="R23" s="3">
         <v>1800</v>
       </c>
       <c r="S23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T23" s="3">
         <v>1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1200</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1400</v>
       </c>
       <c r="W23" s="3">
         <v>1400</v>
       </c>
       <c r="X23" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="Y23" s="3">
         <v>1100</v>
       </c>
       <c r="Z23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>1100</v>
       </c>
       <c r="AD23" s="3">
         <v>1100</v>
       </c>
       <c r="AE23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>1000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
-      <c r="AK23" s="3">
-        <v>0</v>
-      </c>
       <c r="AL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>600</v>
-      </c>
-      <c r="E24" s="3">
-        <v>500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>500</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>600</v>
       </c>
       <c r="L24" s="3">
         <v>600</v>
       </c>
       <c r="M24" s="3">
+        <v>600</v>
+      </c>
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>400</v>
       </c>
       <c r="W24" s="3">
         <v>400</v>
       </c>
       <c r="X24" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y24" s="3">
         <v>300</v>
@@ -2432,43 +2478,46 @@
         <v>300</v>
       </c>
       <c r="AA24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB24" s="3">
         <v>600</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>300</v>
       </c>
       <c r="AC24" s="3">
         <v>300</v>
       </c>
       <c r="AD24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1400</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>-700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,64 +2626,67 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L26" s="3">
         <v>1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="M26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U26" s="3">
         <v>1200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R26" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U26" s="3">
-        <v>1000</v>
       </c>
       <c r="V26" s="3">
         <v>1000</v>
@@ -2643,22 +2695,22 @@
         <v>1000</v>
       </c>
       <c r="X26" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="Y26" s="3">
         <v>800</v>
       </c>
       <c r="Z26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA26" s="3">
         <v>1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>800</v>
       </c>
       <c r="AD26" s="3">
         <v>800</v>
@@ -2667,13 +2719,13 @@
         <v>800</v>
       </c>
       <c r="AF26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG26" s="3">
         <v>600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>100</v>
       </c>
       <c r="AI26" s="3">
         <v>100</v>
@@ -2682,69 +2734,72 @@
         <v>100</v>
       </c>
       <c r="AK26" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL26" s="3">
         <v>700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="M27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U27" s="3">
         <v>1200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U27" s="3">
-        <v>1000</v>
       </c>
       <c r="V27" s="3">
         <v>1000</v>
@@ -2753,22 +2808,22 @@
         <v>1000</v>
       </c>
       <c r="X27" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="Y27" s="3">
         <v>800</v>
       </c>
       <c r="Z27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA27" s="3">
         <v>1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>800</v>
       </c>
       <c r="AD27" s="3">
         <v>800</v>
@@ -2777,13 +2832,13 @@
         <v>800</v>
       </c>
       <c r="AF27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG27" s="3">
         <v>600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>100</v>
       </c>
       <c r="AI27" s="3">
         <v>100</v>
@@ -2792,13 +2847,16 @@
         <v>100</v>
       </c>
       <c r="AK27" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL27" s="3">
         <v>700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2981,8 +3042,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2999,8 +3060,8 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,56 +3339,56 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
-        <v>2500</v>
+      <c r="M32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N32" s="3">
         <v>2500</v>
       </c>
       <c r="O32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>2200</v>
       </c>
       <c r="R32" s="3">
         <v>2200</v>
       </c>
       <c r="S32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1900</v>
-      </c>
-      <c r="W32" s="3">
-        <v>2000</v>
       </c>
       <c r="X32" s="3">
         <v>2000</v>
       </c>
       <c r="Y32" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="Z32" s="3">
         <v>1900</v>
       </c>
       <c r="AA32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB32" s="3">
         <v>3700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1800</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>2000</v>
       </c>
       <c r="AD32" s="3">
         <v>2000</v>
@@ -3330,81 +3400,84 @@
         <v>2000</v>
       </c>
       <c r="AG32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH32" s="3">
         <v>2200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="M33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U33" s="3">
         <v>1200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R33" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U33" s="3">
-        <v>1000</v>
       </c>
       <c r="V33" s="3">
         <v>1000</v>
@@ -3413,22 +3486,22 @@
         <v>1000</v>
       </c>
       <c r="X33" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="Y33" s="3">
         <v>800</v>
       </c>
       <c r="Z33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA33" s="3">
         <v>1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>800</v>
       </c>
       <c r="AD33" s="3">
         <v>800</v>
@@ -3437,13 +3510,13 @@
         <v>800</v>
       </c>
       <c r="AF33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG33" s="3">
         <v>600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>100</v>
       </c>
       <c r="AI33" s="3">
         <v>100</v>
@@ -3452,13 +3525,16 @@
         <v>100</v>
       </c>
       <c r="AK33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL33" s="3">
         <v>700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,64 +3643,67 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="M35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U35" s="3">
         <v>1200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R35" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U35" s="3">
-        <v>1000</v>
       </c>
       <c r="V35" s="3">
         <v>1000</v>
@@ -3633,22 +3712,22 @@
         <v>1000</v>
       </c>
       <c r="X35" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="Y35" s="3">
         <v>800</v>
       </c>
       <c r="Z35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA35" s="3">
         <v>1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>800</v>
       </c>
       <c r="AD35" s="3">
         <v>800</v>
@@ -3657,13 +3736,13 @@
         <v>800</v>
       </c>
       <c r="AF35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG35" s="3">
         <v>600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>100</v>
       </c>
       <c r="AI35" s="3">
         <v>100</v>
@@ -3672,128 +3751,134 @@
         <v>100</v>
       </c>
       <c r="AK35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL35" s="3">
         <v>700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>56600</v>
-      </c>
-      <c r="E41" s="3">
-        <v>68600</v>
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="3">
-        <v>42800</v>
-      </c>
-      <c r="H41" s="3">
-        <v>83000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>79000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>60700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>55600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>33300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>57300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>60900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>57300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>42200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>20200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>19000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>25600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>120400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>162500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>20700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>20300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4023,51 +4113,51 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42" s="3">
         <v>48800</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3">
         <v>49400</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>17800</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>16100</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
@@ -4086,14 +4176,17 @@
       <c r="AJ42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3">
         <v>8300</v>
       </c>
-      <c r="AL42" s="3" t="s">
+      <c r="AM42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4124,8 +4217,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,8 +4443,8 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4422,41 +4521,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>56600</v>
-      </c>
-      <c r="E46" s="3">
-        <v>68600</v>
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G46" s="3">
-        <v>42800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>83000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>79000</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>60700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>40800</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,41 +4634,44 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>13300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>13100</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>13100</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>13200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4642,8 +4747,11 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4674,8 +4782,8 @@
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4683,60 +4791,60 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>9200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>9400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>8700</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>7500</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>62300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>57400</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4746,43 +4854,46 @@
       <c r="AJ48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>6700</v>
       </c>
-      <c r="AL48" s="3" t="s">
+      <c r="AM48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1700</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>1700</v>
       </c>
       <c r="L49" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="M49" s="3">
         <v>1800</v>
@@ -4791,22 +4902,22 @@
         <v>1800</v>
       </c>
       <c r="O49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="P49" s="3">
         <v>1900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3">
-        <v>2000</v>
+      <c r="Q49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S49" s="3">
         <v>2000</v>
       </c>
       <c r="T49" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="U49" s="3">
         <v>2100</v>
@@ -4815,7 +4926,7 @@
         <v>2100</v>
       </c>
       <c r="W49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="X49" s="3">
         <v>2200</v>
@@ -4824,7 +4935,7 @@
         <v>2200</v>
       </c>
       <c r="Z49" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="AA49" s="3">
         <v>2300</v>
@@ -4833,23 +4944,23 @@
         <v>2300</v>
       </c>
       <c r="AC49" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="AD49" s="3">
         <v>2400</v>
       </c>
       <c r="AE49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF49" s="3">
         <v>66100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>56300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2600</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,40 +5199,43 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>29100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>31100</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G52" s="3">
-        <v>30000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>29300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>29700</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>29600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>28800</v>
       </c>
       <c r="L52" s="3">
         <v>28800</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5123,60 +5243,60 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>800</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1100</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>5900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2500</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5186,14 +5306,17 @@
       <c r="AJ52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>3400</v>
       </c>
-      <c r="AL52" s="3" t="s">
+      <c r="AM52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>532400</v>
-      </c>
-      <c r="E54" s="3">
-        <v>537900</v>
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="3">
-        <v>516800</v>
-      </c>
-      <c r="H54" s="3">
-        <v>539500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>541600</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>513300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>510600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>500200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>471600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>473800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>460300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>457900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3">
         <v>420700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>423300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>418300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>406300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>402200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>414800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>377200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>352600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>360000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>368700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>353300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>345000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>354000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2481700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2299400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>356000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>333700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>227900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>223900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>219500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,41 +5622,42 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>464100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>472600</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="3">
-        <v>455000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>478000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>472000</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>444400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>444500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>434700</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -5602,41 +5733,44 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>800</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>800</v>
       </c>
       <c r="L58" s="3">
+        <v>800</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5712,8 +5846,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5744,8 +5881,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5753,39 +5890,39 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>2700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>2400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>3000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5801,8 +5938,8 @@
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG59" s="3">
         <v>0</v>
@@ -5822,41 +5959,44 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>465400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>473700</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G60" s="3">
-        <v>456600</v>
-      </c>
-      <c r="H60" s="3">
-        <v>479400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>472800</v>
-      </c>
-      <c r="J60" s="3">
-        <v>445200</v>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>445200</v>
       </c>
       <c r="L60" s="3">
+        <v>445200</v>
+      </c>
+      <c r="M60" s="3">
         <v>435700</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,8 +6072,11 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5953,22 +6096,22 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>11700</v>
+      </c>
+      <c r="L61" s="3">
+        <v>11100</v>
+      </c>
+      <c r="M61" s="3">
         <v>11000</v>
       </c>
-      <c r="J61" s="3">
-        <v>11700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>11100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>11000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>1500</v>
@@ -5977,7 +6120,7 @@
         <v>1500</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -5989,11 +6132,11 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>2500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -6001,11 +6144,11 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>2500</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -6013,20 +6156,20 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>2500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>75200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10300</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -6042,41 +6185,44 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>5600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>4600</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G62" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
-        <v>5300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,41 +6637,44 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>471000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>478300</v>
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="3">
-        <v>460700</v>
-      </c>
-      <c r="H66" s="3">
-        <v>484300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>488000</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>462200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>460300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>450800</v>
       </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
       <c r="N66" s="3">
         <v>0</v>
       </c>
@@ -6535,48 +6693,48 @@
       <c r="S66" s="3">
         <v>0</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="T66" s="3">
+        <v>0</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>363500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>314900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>311200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>2195900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2040900</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6586,14 +6744,17 @@
       <c r="AJ66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL66" s="3">
         <v>199700</v>
       </c>
-      <c r="AL66" s="3" t="s">
+      <c r="AM66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,8 +7243,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7104,8 +7278,8 @@
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
+      <c r="M72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N72" s="3">
         <v>0</v>
@@ -7113,51 +7287,51 @@
       <c r="O72" s="3">
         <v>0</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>35200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>30800</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>27500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>24500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7176,14 +7350,17 @@
       <c r="AJ72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>21900</v>
       </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AM72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>61400</v>
-      </c>
-      <c r="E76" s="3">
-        <v>59600</v>
-      </c>
-      <c r="F76" s="3">
-        <v>56000</v>
-      </c>
-      <c r="G76" s="3">
-        <v>56000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>55200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>53600</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>51100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>44200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>43800</v>
-      </c>
-      <c r="T76" s="3">
-        <v>42800</v>
       </c>
       <c r="U76" s="3">
         <v>42800</v>
       </c>
       <c r="V76" s="3">
+        <v>42800</v>
+      </c>
+      <c r="W76" s="3">
         <v>42700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>41700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>40500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>37700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>35800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>34500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>33800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>285800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>258500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>31100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>19800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,179 +7921,185 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="M81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U81" s="3">
         <v>1200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R81" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U81" s="3">
-        <v>1000</v>
       </c>
       <c r="V81" s="3">
         <v>1000</v>
@@ -7913,22 +8108,22 @@
         <v>1000</v>
       </c>
       <c r="X81" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="Y81" s="3">
         <v>800</v>
       </c>
       <c r="Z81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA81" s="3">
         <v>1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>800</v>
       </c>
       <c r="AD81" s="3">
         <v>800</v>
@@ -7937,13 +8132,13 @@
         <v>800</v>
       </c>
       <c r="AF81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG81" s="3">
         <v>600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>100</v>
       </c>
       <c r="AI81" s="3">
         <v>100</v>
@@ -7952,13 +8147,16 @@
         <v>100</v>
       </c>
       <c r="AK81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL81" s="3">
         <v>700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8029,8 +8228,8 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8689,8 +8906,8 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -8767,8 +8984,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8839,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9169,8 +9399,8 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9759,8 +10005,8 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9837,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9979,8 +10231,8 @@
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -10055,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
